--- a/questionnaire_templates/007_hieroglyph_selection_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/007_hieroglyph_selection_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'the_ankh'}</t>
+          <t>the_ankh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'The Ankh'}</t>
+          <t>The Ankh</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'the_djed'}</t>
+          <t>the_djed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'The Djed'}</t>
+          <t>The Djed</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'the_eye_of_ra'}</t>
+          <t>the_eye_of_ra</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'The Eye of Ra'}</t>
+          <t>The Eye of Ra</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'the_scarab'}</t>
+          <t>the_scarab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'The Scarab'}</t>
+          <t>The Scarab</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'the_was'}</t>
+          <t>the_was</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'The Was'}</t>
+          <t>The Was</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'the_ankh'}</t>
+          <t>the_ankh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'The Ankh'}</t>
+          <t>The Ankh</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'the_djed'}</t>
+          <t>the_djed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'The Djed'}</t>
+          <t>The Djed</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'the_eye_of_ra'}</t>
+          <t>the_eye_of_ra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'The Eye of Ra'}</t>
+          <t>The Eye of Ra</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'the_scarab'}</t>
+          <t>the_scarab</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'The Scarab'}</t>
+          <t>The Scarab</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'the_was'}</t>
+          <t>the_was</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'The Was'}</t>
+          <t>The Was</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'the_ankh'}</t>
+          <t>the_ankh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'The Ankh'}</t>
+          <t>The Ankh</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'the_djed'}</t>
+          <t>the_djed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'The Djed'}</t>
+          <t>The Djed</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'the_eye_of_ra'}</t>
+          <t>the_eye_of_ra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'The Eye of Ra'}</t>
+          <t>The Eye of Ra</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'the_scarab'}</t>
+          <t>the_scarab</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'The Scarab'}</t>
+          <t>The Scarab</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'the_was'}</t>
+          <t>the_was</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'The Was'}</t>
+          <t>The Was</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'arabic'}</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Arabic'}</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
